--- a/exports/IRFC_full_report.xlsx
+++ b/exports/IRFC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>2.48</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>23.55</v>
+        <v>23.35</v>
       </c>
       <c r="I2" t="n">
         <v>23.35304242071949</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>2.39</v>
+        <v>1.52</v>
       </c>
       <c r="L2" t="n">
         <v>0.65</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>3.66</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44634.38541666666</v>
+        <v>44634.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>21.8</v>
+        <v>22.05</v>
       </c>
       <c r="I3" t="n">
         <v>21.94436905800059</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.83333333333334</v>
+        <v>52</v>
       </c>
       <c r="K3" t="n">
-        <v>6.64</v>
+        <v>5.57</v>
       </c>
       <c r="L3" t="n">
         <v>1.07</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>4.16</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44645.55208333334</v>
+        <v>44648.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>22.15</v>
+        <v>21.8</v>
       </c>
       <c r="I4" t="n">
         <v>21.86326321213302</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>-1.13</v>
       </c>
       <c r="L4" t="n">
         <v>1.36</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.11</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44656.55208333334</v>
+        <v>44657.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>22.05</v>
+        <v>22.2</v>
       </c>
       <c r="I5" t="n">
         <v>22.17110374341968</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.15</v>
+        <v>-1.83</v>
       </c>
       <c r="L5" t="n">
         <v>2.29</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>3.74</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>22.05</v>
+        <v>21.75</v>
       </c>
       <c r="I6" t="n">
         <v>21.82565610547524</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.68</v>
+        <v>-2.03</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>2.48</v>
       </c>
       <c r="M6" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
         <v>0.68</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>3.46</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44753.38541666666</v>
+        <v>44753.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>20.05</v>
+        <v>20.25</v>
       </c>
       <c r="I7" t="n">
         <v>20.13541031985423</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>66</v>
+        <v>66.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>7.82</v>
+        <v>6.9</v>
       </c>
       <c r="L7" t="n">
         <v>0.92</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>3.25</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44818.55208333334</v>
+        <v>44819.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>22.85</v>
+        <v>22.3</v>
       </c>
       <c r="I8" t="n">
         <v>22.30580780428676</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>65</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>12.84</v>
+        <v>10.12</v>
       </c>
       <c r="L8" t="n">
         <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.89</v>
+        <v>1.53</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>2.41</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.05</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44858.76041666666</v>
+        <v>44859.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>21.65</v>
+        <v>21.95</v>
       </c>
       <c r="I9" t="n">
         <v>21.68029773230191</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39.375</v>
+        <v>40</v>
       </c>
       <c r="K9" t="n">
-        <v>2.91</v>
+        <v>1.57</v>
       </c>
       <c r="L9" t="n">
         <v>0.9</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>3.4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>32.2</v>
+        <v>30.75</v>
       </c>
       <c r="I10" t="n">
         <v>31.37758436915399</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K10" t="n">
-        <v>46.7</v>
+        <v>40.09</v>
       </c>
       <c r="L10" t="n">
         <v>2.05</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>14.2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44915.38541666666</v>
+        <v>44915.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>33.55</v>
+        <v>35.7</v>
       </c>
       <c r="I11" t="n">
         <v>34.37052382006189</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.109999999999999</v>
+        <v>-16.1</v>
       </c>
       <c r="L11" t="n">
-        <v>12.85</v>
+        <v>16.75</v>
       </c>
       <c r="M11" t="n">
         <v>0.74</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>12.58</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>31.35</v>
+        <v>28.85</v>
       </c>
       <c r="I12" t="n">
         <v>31.20946409071568</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-12.18</v>
+        <v>-19.19</v>
       </c>
       <c r="L12" t="n">
-        <v>13.45</v>
+        <v>19.89</v>
       </c>
       <c r="M12" t="n">
-        <v>-0</v>
+        <v>1.28</v>
       </c>
       <c r="N12" t="n">
-        <v>8.119999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="O12" t="n">
         <v>8.84</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>20.11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>32.8</v>
+        <v>33.6</v>
       </c>
       <c r="I13" t="n">
         <v>32.98005199416598</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>-13.69</v>
+        <v>-16.46</v>
       </c>
       <c r="L13" t="n">
-        <v>15.42</v>
+        <v>18.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.62</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>10.46</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>32.05</v>
+        <v>30.8</v>
       </c>
       <c r="I14" t="n">
         <v>31.57008943474277</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.61</v>
+        <v>-8.33</v>
       </c>
       <c r="L14" t="n">
-        <v>5.65</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>0.76</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.56</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44986.55208333334</v>
+        <v>44987.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>27.3</v>
+        <v>28.7</v>
       </c>
       <c r="I15" t="n">
         <v>28.49331238850338</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>11.36</v>
+        <v>6.82</v>
       </c>
       <c r="L15" t="n">
         <v>10.71</v>
@@ -1296,7 +1475,7 @@
         <v>8.32</v>
       </c>
       <c r="N15" t="n">
-        <v>1.87</v>
+        <v>4.58</v>
       </c>
       <c r="O15" t="n">
         <v>-2.18</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>26.55</v>
+        <v>26.05</v>
       </c>
       <c r="I16" t="n">
         <v>26.46981062134724</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.49</v>
+        <v>-9.23</v>
       </c>
       <c r="L16" t="n">
-        <v>8.01</v>
+        <v>9.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="O16" t="n">
         <v>4.58</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.92</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>26.45</v>
+        <v>26.9</v>
       </c>
       <c r="I17" t="n">
         <v>26.8391041483894</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.54</v>
+        <v>-3.26</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="M17" t="n">
         <v>0.58</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45055.38541666666</v>
+        <v>45055.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>33.45</v>
+        <v>32.85</v>
       </c>
       <c r="I18" t="n">
         <v>33.04818824482024</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>24.35</v>
+        <v>22.12</v>
       </c>
       <c r="L18" t="n">
         <v>1.67</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.89</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45084.38541666666</v>
+        <v>45084.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>33.25</v>
+        <v>33.9</v>
       </c>
       <c r="I19" t="n">
         <v>33.33321288894867</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.22</v>
+        <v>-3.2</v>
       </c>
       <c r="L19" t="n">
         <v>5.48</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.81</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45190.38541666666</v>
+        <v>45190.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>74.84999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="I20" t="n">
         <v>74.84780314937166</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>105.8333333333333</v>
+        <v>106</v>
       </c>
       <c r="K20" t="n">
-        <v>120.8</v>
+        <v>119.76</v>
       </c>
       <c r="L20" t="n">
         <v>5.6</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>13.62</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>76.3</v>
+        <v>80.05</v>
       </c>
       <c r="I21" t="n">
         <v>77.17394504903919</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.42</v>
+        <v>-7.45</v>
       </c>
       <c r="L21" t="n">
-        <v>5.64</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M21" t="n">
         <v>1.67</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.99</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>77.05</v>
+        <v>72.45</v>
       </c>
       <c r="I22" t="n">
         <v>73.74627134161986</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.75</v>
+        <v>-9.49</v>
       </c>
       <c r="L22" t="n">
-        <v>5.31</v>
+        <v>10.06</v>
       </c>
       <c r="M22" t="n">
         <v>1.93</v>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>6.23</v>
       </c>
       <c r="O22" t="n">
         <v>3.8</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.68</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>73.15000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>76.14821887532064</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.97</v>
+        <v>-6.42</v>
       </c>
       <c r="L23" t="n">
         <v>7.59</v>
@@ -1752,7 +2027,7 @@
         <v>2.22</v>
       </c>
       <c r="N23" t="n">
-        <v>3.49</v>
+        <v>4.99</v>
       </c>
       <c r="O23" t="n">
         <v>-6.23</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>153.75</v>
+        <v>138.4</v>
       </c>
       <c r="I24" t="n">
         <v>153.2014974561513</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>87</v>
       </c>
       <c r="K24" t="n">
-        <v>99.42</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>5.71</v>
@@ -1809,7 +2096,7 @@
         <v>3.44</v>
       </c>
       <c r="N24" t="n">
-        <v>7.83</v>
+        <v>13.24</v>
       </c>
       <c r="O24" t="n">
         <v>4.99</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>19.62</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45336.55208333334</v>
+        <v>45337.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>154.2</v>
+        <v>158.45</v>
       </c>
       <c r="I25" t="n">
         <v>158.2426318537149</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>-11.42</v>
+        <v>-14.49</v>
       </c>
       <c r="L25" t="n">
-        <v>13.73</v>
+        <v>16.69</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="N25" t="n">
         <v>16.75</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>17.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>141</v>
+        <v>136.6</v>
       </c>
       <c r="I26" t="n">
         <v>140.1348024379152</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K26" t="n">
-        <v>-11.01</v>
+        <v>-13.79</v>
       </c>
       <c r="L26" t="n">
-        <v>11.86</v>
+        <v>14.39</v>
       </c>
       <c r="M26" t="n">
         <v>0.75</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.25</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45373.55208333334</v>
+        <v>45377.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>141.05</v>
+        <v>146.4</v>
       </c>
       <c r="I27" t="n">
         <v>142.2529315554798</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.26</v>
+        <v>-7.17</v>
       </c>
       <c r="L27" t="n">
-        <v>6.77</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>2.85</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.34</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>155.1</v>
+        <v>150.1</v>
       </c>
       <c r="I28" t="n">
         <v>150.7092718904767</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K28" t="n">
-        <v>5.94</v>
+        <v>2.53</v>
       </c>
       <c r="L28" t="n">
         <v>7.58</v>
@@ -2037,7 +2372,7 @@
         <v>5.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.37</v>
+        <v>3.64</v>
       </c>
       <c r="O28" t="n">
         <v>3.44</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>9.5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>157.2</v>
+        <v>163.9</v>
       </c>
       <c r="I29" t="n">
         <v>157.8075813918288</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.73</v>
+        <v>-9.19</v>
       </c>
       <c r="L29" t="n">
-        <v>6.46</v>
+        <v>9.43</v>
       </c>
       <c r="M29" t="n">
         <v>0.84</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>189.7</v>
+        <v>169.8</v>
       </c>
       <c r="I30" t="n">
         <v>172.5840663821426</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>15.74</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>4.15</v>
+        <v>7.75</v>
       </c>
       <c r="M30" t="n">
         <v>1.27</v>
       </c>
       <c r="N30" t="n">
-        <v>2.27</v>
+        <v>12.1</v>
       </c>
       <c r="O30" t="n">
         <v>7.79</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>17.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>177.69</v>
+        <v>186.99</v>
       </c>
       <c r="I31" t="n">
         <v>179.8719377892367</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.65</v>
+        <v>-10.12</v>
       </c>
       <c r="L31" t="n">
         <v>11.31</v>
@@ -2208,7 +2579,7 @@
         <v>2.99</v>
       </c>
       <c r="N31" t="n">
-        <v>4.01</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
         <v>-12.1</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>205</v>
+        <v>192.38</v>
       </c>
       <c r="I32" t="n">
         <v>199.8977366654428</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>9.630000000000001</v>
+        <v>2.88</v>
       </c>
       <c r="L32" t="n">
-        <v>4.75</v>
+        <v>12.21</v>
       </c>
       <c r="M32" t="n">
         <v>2.27</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
         <v>5.8</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.72</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45594.38541666666</v>
+        <v>45594.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>142.4</v>
+        <v>144.55</v>
       </c>
       <c r="I33" t="n">
         <v>144.5257658723137</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>98</v>
+        <v>98.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>25.98</v>
+        <v>24.86</v>
       </c>
       <c r="L33" t="n">
         <v>8.640000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>8.98</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>145.11</v>
+        <v>141.74</v>
       </c>
       <c r="I34" t="n">
         <v>144.3727433819387</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>0.39</v>
+        <v>-1.94</v>
       </c>
       <c r="L34" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
         <v>0.85</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.41</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>147.1</v>
+        <v>150.28</v>
       </c>
       <c r="I35" t="n">
         <v>149.2910483951957</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.78</v>
+        <v>-6.03</v>
       </c>
       <c r="L35" t="n">
-        <v>6.32</v>
+        <v>7.03</v>
       </c>
       <c r="M35" t="n">
         <v>4.72</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.01</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>156.4</v>
+        <v>153.89</v>
       </c>
       <c r="I36" t="n">
         <v>154.2593910589386</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>4.07</v>
+        <v>2.4</v>
       </c>
       <c r="L36" t="n">
         <v>2.95</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45656.38541666666</v>
+        <v>45656.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>146.46</v>
+        <v>157.9</v>
       </c>
       <c r="I37" t="n">
         <v>154.3045910596796</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>4.83</v>
+        <v>-2.61</v>
       </c>
       <c r="L37" t="n">
-        <v>1.94</v>
+        <v>2.67</v>
       </c>
       <c r="M37" t="n">
         <v>0.51</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>11.24</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>146</v>
+        <v>142.48</v>
       </c>
       <c r="I38" t="n">
         <v>143.5161066557589</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.54</v>
+        <v>-9.77</v>
       </c>
       <c r="L38" t="n">
-        <v>8.359999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="M38" t="n">
         <v>5.01</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.68</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>137.1</v>
+        <v>144.57</v>
       </c>
       <c r="I39" t="n">
         <v>139.6520542571866</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>3.78</v>
+        <v>-1.47</v>
       </c>
       <c r="L39" t="n">
         <v>2.82</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>10.37</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>141.4</v>
+        <v>135.22</v>
       </c>
       <c r="I40" t="n">
         <v>139.6253730345009</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.19</v>
+        <v>-6.47</v>
       </c>
       <c r="L40" t="n">
-        <v>6.81</v>
+        <v>7.69</v>
       </c>
       <c r="M40" t="n">
-        <v>1.19</v>
+        <v>2.87</v>
       </c>
       <c r="N40" t="n">
         <v>6.35</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.14</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>120.6</v>
+        <v>123.34</v>
       </c>
       <c r="I41" t="n">
         <v>121.6615868319364</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K41" t="n">
-        <v>10.81</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L41" t="n">
         <v>3.68</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.58</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45743.38541666666</v>
+        <v>45743.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>126.1</v>
+        <v>124.59</v>
       </c>
       <c r="I42" t="n">
         <v>124.9349725648404</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="L42" t="n">
         <v>5.49</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7.5</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>128.33</v>
+        <v>129.36</v>
       </c>
       <c r="I43" t="n">
         <v>128.5033603008903</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-3</v>
+        <v>-3.83</v>
       </c>
       <c r="L43" t="n">
-        <v>3.94</v>
+        <v>4.29</v>
       </c>
       <c r="M43" t="n">
         <v>2.57</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.86</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>128.94</v>
+        <v>128</v>
       </c>
       <c r="I44" t="n">
         <v>128.1200936584861</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.32</v>
+        <v>-1.05</v>
       </c>
       <c r="L44" t="n">
         <v>2.43</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.71</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>123.58</v>
+        <v>125.44</v>
       </c>
       <c r="I45" t="n">
         <v>124.2883049127546</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K45" t="n">
-        <v>3.45</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
         <v>1.45</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>7.75</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>140.5</v>
+        <v>138.36</v>
       </c>
       <c r="I46" t="n">
         <v>140.0076453078241</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>12.01</v>
+        <v>10.3</v>
       </c>
       <c r="L46" t="n">
         <v>1.71</v>
       </c>
       <c r="M46" t="n">
-        <v>0.79</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
         <v>3.47</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.6</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>140.06</v>
+        <v>141.81</v>
       </c>
       <c r="I47" t="n">
         <v>140.2322000249804</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.23</v>
+        <v>-2.49</v>
       </c>
       <c r="L47" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
         <v>1.2</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>4.95</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>136</v>
+        <v>135.14</v>
       </c>
       <c r="I48" t="n">
         <v>135.5972262183249</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.1</v>
+        <v>-4.7</v>
       </c>
       <c r="L48" t="n">
-        <v>4.63</v>
+        <v>4.8</v>
       </c>
       <c r="M48" t="n">
         <v>0.18</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>3.71</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>120.89</v>
+        <v>125.39</v>
       </c>
       <c r="I49" t="n">
         <v>123.1757497385957</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>52</v>
+        <v>52.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>10.54</v>
+        <v>7.21</v>
       </c>
       <c r="L49" t="n">
         <v>2.12</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.41</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>125.59</v>
+        <v>125.15</v>
       </c>
       <c r="I50" t="n">
         <v>125.4208068100919</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
-        <v>0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="L50" t="n">
         <v>3.81</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.58</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45937.38541666666</v>
+        <v>45937.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>126.18</v>
+        <v>127.4</v>
       </c>
       <c r="I51" t="n">
         <v>126.7822326821697</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.82</v>
+        <v>-1.8</v>
       </c>
       <c r="L51" t="n">
         <v>1.88</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>4.29</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>122.3</v>
+        <v>120.86</v>
       </c>
       <c r="I52" t="n">
         <v>122.0216786926673</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>28</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-4</v>
+        <v>-5.13</v>
       </c>
       <c r="L52" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="M52" t="n">
         <v>1.11</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>3.32</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>114.29</v>
+        <v>116.85</v>
       </c>
       <c r="I53" t="n">
         <v>114.8706707017752</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K53" t="n">
-        <v>5.44</v>
+        <v>3.32</v>
       </c>
       <c r="L53" t="n">
         <v>2.18</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.2</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46030.38541666666</v>
+        <v>46030.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>125.06</v>
+        <v>123.81</v>
       </c>
       <c r="I54" t="n">
         <v>123.9021054269356</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>7.03</v>
+        <v>5.96</v>
       </c>
       <c r="L54" t="n">
         <v>2.36</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.55</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>93</v>
+        <v>96.23</v>
       </c>
       <c r="I55" t="n">
         <v>95.99376158673033</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>75</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>24.88</v>
+        <v>22.28</v>
       </c>
       <c r="L55" t="n">
         <v>1.28</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46108.55208333334</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>92.40000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>89.36552352294623</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.98</v>
+        <v>-7.7</v>
       </c>
       <c r="L56" t="n">
-        <v>4.49</v>
+        <v>7.91</v>
       </c>
       <c r="M56" t="n">
-        <v>0.26</v>
+        <v>1.03</v>
       </c>
       <c r="N56" t="n">
-        <v>2.8</v>
+        <v>5.47</v>
       </c>
       <c r="O56" t="n">
         <v>2.22</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>92.97</v>
+        <v>98.17</v>
       </c>
       <c r="I57" t="n">
         <v>94.89251351659499</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.67</v>
+        <v>-10.53</v>
       </c>
       <c r="L57" t="n">
-        <v>5.37</v>
+        <v>10.89</v>
       </c>
       <c r="M57" t="n">
-        <v>3.98</v>
+        <v>5.2</v>
       </c>
       <c r="N57" t="n">
-        <v>5.44</v>
+        <v>6.81</v>
       </c>
       <c r="O57" t="n">
         <v>-5.47</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>103.2</v>
+        <v>100.83</v>
       </c>
       <c r="I58" t="n">
         <v>102.2430346901441</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K58" t="n">
-        <v>5.12</v>
+        <v>2.71</v>
       </c>
       <c r="L58" t="n">
         <v>1.96</v>
@@ -3747,7 +4442,7 @@
         <v>3.21</v>
       </c>
       <c r="N58" t="n">
-        <v>2.65</v>
+        <v>3.41</v>
       </c>
       <c r="O58" t="n">
         <v>6.81</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>5.89</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I59" t="n">
         <v>97.50316625923168</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K59" t="n">
-        <v>4.79</v>
+        <v>2.81</v>
       </c>
       <c r="L59" t="n">
         <v>2.78</v>
       </c>
       <c r="M59" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="N59" t="n">
         <v>2.76</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.01</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46196.55208333334</v>
+        <v>46197.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>98.34999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I60" t="n">
         <v>96.7100709972725</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K60" t="n">
-        <v>0.36</v>
+        <v>-3.88</v>
       </c>
       <c r="L60" t="n">
-        <v>1.17</v>
+        <v>5.18</v>
       </c>
       <c r="M60" t="n">
-        <v>0.99</v>
+        <v>4.42</v>
       </c>
       <c r="N60" t="n">
-        <v>2.48</v>
+        <v>6.53</v>
       </c>
       <c r="O60" t="n">
         <v>1.04</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.38</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>89.02</v>
+        <v>89.95</v>
       </c>
       <c r="I61" t="n">
         <v>89.53080990553275</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K61" t="n">
-        <v>5.5</v>
+        <v>4.51</v>
       </c>
       <c r="L61" t="n">
         <v>0.58</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>3.44</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>87.38</v>
+        <v>86.36</v>
       </c>
       <c r="I62" t="n">
         <v>87.17906806095202</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.86</v>
+        <v>-3.99</v>
       </c>
       <c r="L62" t="n">
         <v>4.17</v>
       </c>
       <c r="M62" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="N62" t="n">
-        <v>0.89</v>
+        <v>1.44</v>
       </c>
       <c r="O62" t="n">
         <v>1.44</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>3.43</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>77.45</v>
+        <v>78.92</v>
       </c>
       <c r="I63" t="n">
         <v>78.41010279679311</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K63" t="n">
-        <v>10.32</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L63" t="n">
         <v>1.39</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.61</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>77.25</v>
+        <v>74.03</v>
       </c>
       <c r="I64" t="n">
         <v>76.27573877942807</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.12</v>
+        <v>-6.2</v>
       </c>
       <c r="L64" t="n">
-        <v>4.21</v>
+        <v>6.41</v>
       </c>
       <c r="M64" t="n">
-        <v>0.13</v>
+        <v>1.02</v>
       </c>
       <c r="N64" t="n">
-        <v>2.48</v>
+        <v>3.75</v>
       </c>
       <c r="O64" t="n">
         <v>2.83</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,12 @@
       <c r="Q65" t="n">
         <v>6</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7036,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.7</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7046,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7056,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105.8</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7066,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7076,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7086,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.5</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="11">
@@ -6341,7 +7126,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.94</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7136,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.460000000000001</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7146,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7156,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>120.8</v>
+        <v>119.76</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7166,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.4</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7176,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.67</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7186,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.94</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="21">
@@ -6411,7 +7196,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.42</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="22">
@@ -6421,7 +7206,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -6431,7 +7216,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -6441,7 +7226,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="25">
@@ -6461,7 +7246,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.36</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="27">
@@ -6481,7 +7266,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
